--- a/resultsTimes.xlsx
+++ b/resultsTimes.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.91</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="3">
@@ -457,17 +457,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.18</v>
+        <v>87.73999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gemma3:4b</t>
+          <t>gpt-oss:20b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.79</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.71</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.74</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.03</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -507,17 +507,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.58</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gemma3:4b</t>
+          <t>gpt-oss:20b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.32</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.09</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36.24</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23.94</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="13">
@@ -557,17 +557,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22.46</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gemma3:4b</t>
+          <t>gpt-oss:20b</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.13</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12.21</v>
+        <v>30.88</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>68.51000000000001</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="17">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.22</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="18">
@@ -607,17 +607,17 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12.41</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gemma3:4b</t>
+          <t>gpt-oss:20b</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12.1</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.27</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="21">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>37.41</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="22">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.33</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="23">
@@ -657,17 +657,17 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13.18</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gemma3:4b</t>
+          <t>gpt-oss:20b</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13.54</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="25">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27.07</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="26">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>47.09</v>
+        <v>28.61</v>
       </c>
     </row>
   </sheetData>
